--- a/光伏配储项目/电价数据/2026/八一站.xlsx
+++ b/光伏配储项目/电价数据/2026/八一站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5541200000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.65242</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.05058</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.17353</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.14985</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.11549</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.98927</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.99325</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.65211</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.7049500000000001</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.6377</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.97734</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.97733</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.97339</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.6309900000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.9847899999999999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.9807400000000001</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.96529</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.97594</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.66739</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.9819099999999999</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.65992</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.98111</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.9866900000000001</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.68791</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.01137</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.09632</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.88235</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6921799999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6867000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.75358</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7766900000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.04262</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.03094</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.12247</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75859</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.71846</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.79131</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9796900000000001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34221</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52971</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7805599999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.78875</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.7630399999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9558300000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.92022</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.07197</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.34668</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.1929</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.22402</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74624</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.24689</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.19188</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10455</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.25125</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.54751</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.2091</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.27729</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.49597</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.33438</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.25556</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.43484</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.3759</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.30782</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81535</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.18804</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04452</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.1817</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51559</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.72765</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.6294999999999999</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.70197</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.60815</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.60003</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.68676</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.65037</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.64612</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.63773</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.69463</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.96113</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.29941</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.95339</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.70582</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.59945</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.6604500000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.56925</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.95716</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.17062</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.79588</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.12932</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.05631</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.01625</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7237899999999999</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.55433</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5764400000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.69538</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.19185</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.25956</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.50841</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.18903</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.66244</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09008</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8407899999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.27399</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.16369</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29456</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62536</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.65013</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6263500000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.20182</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.19674</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.20456</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.19797</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.99576</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18439</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19944</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19512</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67464</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.19159</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2075</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.25469</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.55237</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.46637</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.19698</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50699</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26595</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7539199999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76402</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91434</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.68935</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.83812</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.8140499999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.6024700000000001</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.6780700000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5904199999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.27402</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.80116</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.79261</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.7504700000000001</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.67992</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.81728</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.6372599999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.79596</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.58187</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.67649</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.59693</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.66879</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.64227</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.6261100000000001</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.64311</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.64698</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.57586</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.70516</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83813</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.11799</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.88039</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7632100000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71227</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6085900000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42622</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.74276</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.1809</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.55426</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.69333</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.18848</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.6627</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19437</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.19331</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.8061799999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.96835</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.19461</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.19493</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.90546</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56262</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41449</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47671</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67886</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18466</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.04897</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.19349</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.43207</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.27446</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.19292</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22206</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21356</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.44003</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.28864</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.66617</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.20838</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.20721</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.06516</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.0989</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.11977</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.10583</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.23321</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.2766</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.01882</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.76725</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.7244700000000001</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53715</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.16618</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.84697</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8322000000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.8027300000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.97296</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.6558200000000001</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.7710399999999999</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.6662400000000001</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.84054</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.79644</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.7337899999999999</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.65166</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.64899</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.56725</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.49098</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.49451</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.65974</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.65363</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.7640399999999999</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.6419900000000001</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.60917</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.56985</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.52611</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6853400000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72337</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.94048</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.19111</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.33409</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.85853</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.57644</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67125</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.91143</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.88923</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.18524</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44601</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77802</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.98154</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.24046</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.70594</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11896</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52908</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.49136</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.66723</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.02057</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.12296</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.26298</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.19388</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.09334</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.00959</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03349</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9974400000000001</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.28833</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.47087</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.81057</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.37664</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.22643</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.8627100000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10085</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18207</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13199</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.18307</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28047</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34143</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.18294</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.2945</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20111</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19081</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18608</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21149</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22138</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.20704</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.18419</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.18737</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5300499999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.74329</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32192</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74888</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52915</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46127</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.72629</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8593</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.71129</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.73666</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.85685</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71485</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5584199999999999</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55747</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54608</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47732</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55504</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.49017</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.64686</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51052</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49033</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49071</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.51196</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51119</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49047</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34423</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.21399</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.99117</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.00641</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5977100000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.73548</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.6936</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.64524</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.6928799999999999</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.6806599999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.67983</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.97645</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.68604</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.6861799999999999</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.6792100000000001</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.6797799999999999</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.68004</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07464</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04282</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08381999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13074</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04461</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04669</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04657</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00347</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04636</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04626</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.26592</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28293</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.71401</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.69156</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.70075</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.69249</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.69211</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33453</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.68082</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.59992</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27369</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.76051</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8966799999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.69043</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6644800000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.68231</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7646900000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.96175</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48348</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7462000000000001</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.9086799999999999</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.67477</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54579</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48468</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45542</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09257</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74275</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.7464400000000001</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6518699999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6122300000000001</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7379199999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79059</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78955</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60891</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.02854</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.42684</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.85794</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.45611</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.33869</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.80799</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40179</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.06152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42212</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.78397</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46154</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.78489</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80091</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78546</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8790800000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50247</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41201</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46066</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21912</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54138</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.7304299999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.7083700000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.70053</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.7038099999999999</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.70675</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.7074400000000001</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.6992699999999999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.58325</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.5945499999999999</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.69194</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.68128</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.68028</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.67871</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.6797300000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.69459</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.6801900000000001</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.68016</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.5852200000000001</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.7278600000000001</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.58368</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60017</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5646</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6668500000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07831</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.64588</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50792</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57555</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59714</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00808</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34185</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.31027</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27338</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5608200000000001</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8005099999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5758799999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6554500000000001</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55702</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.98346</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.78543</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7342000000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6497000000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.58208</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.01588</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.07007</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.72453</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.68384</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.74718</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.67106</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.7176399999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.82274</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.70716</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.7166</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.60519</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.58949</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.7164700000000001</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.75037</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.7269600000000001</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.74779</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.78049</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.7506</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.7889400000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.75425</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.75718</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.75613</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.74695</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.7425499999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.72772</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.74254</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.7185199999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.69328</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.72557</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.69737</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.70721</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.6979500000000001</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.69213</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.6880299999999999</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.5825900000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95611</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.6766</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.80804</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.7833300000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.83847</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.67901</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.6858200000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.61686</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.65588</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.66028</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.52949</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.62782</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.74636</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.8952100000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.14593</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9399400000000001</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5578500000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12358</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.86376</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9716900000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.88087</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.6516000000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.83088</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.67672</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.53203</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.89896</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.13009</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.7995099999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.22812</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8035399999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8344400000000001</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.86513</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7569</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19977</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51702</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.80165</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.76644</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.18637</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.93249</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.65534</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.71274</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.57426</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.6313</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.9203300000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.59573</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.7079</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.46073</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.38434</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.35231</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.64195</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.13327</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.53794</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6139</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52484</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7616799999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.09298</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09163</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.94257</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99388</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.94772</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18457</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.17959</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8841100000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.17985</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.62695</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99273</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.0369</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.17976</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9730599999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.01386</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.60396</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.94576</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00273</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.11002</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.90715</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.89478</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.11941</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.60274</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9815700000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.01785</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.75579</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33857</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.7767200000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.64049</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.6419199999999999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.6207699999999999</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.65255</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.80338</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.64949</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.61164</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.64477</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.61346</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83531</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.72236</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.7548400000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.68569</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.01107</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.24201</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.68779</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.69035</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.62779</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.62952</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.68499</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.78672</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.7673099999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.68774</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.56984</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.56389</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.57372</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.57602</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.69153</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.63342</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.6200800000000001</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.62076</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.6197999999999999</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.6194700000000001</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.59357</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.5071</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.54506</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.76173</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.6858300000000001</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.68862</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.6832</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.7053400000000001</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.61253</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.6482599999999999</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.5329700000000001</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.5324099999999999</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.45768</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.65777</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.68924</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.68591</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.66649</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.6096699999999999</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.6043200000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55784</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47276</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48677</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70469</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60533</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62678</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84741</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26857</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16383</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.85063</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45048</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42858</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70039</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.93847</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16552</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11942</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01617</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54132</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49696</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44702</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56537</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.5713200000000001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.56843</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.5713200000000001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.53484</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.6610900000000001</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.46157</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.45955</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.5353600000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.59465</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.6627000000000001</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.6176900000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.69071</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.99258</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.33401</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.23106</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9994500000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98817</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98975</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56219</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55129</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94428</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08407</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79041</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01109</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77442</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65497</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.6477</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71501</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79745</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29527</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.77322</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.36143</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.49727</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.16716</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.99437</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.6605</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63041</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66404</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67741</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67247</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64946</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67395</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20677</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70689</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78867</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70418</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71196</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72011</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63912</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.7544</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.0195</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12896</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69802</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70645</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70023</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77985</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73001</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8192</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.67089</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.19201</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.69086</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.56657</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.59987</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34473</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.5609700000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.71099</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.29519</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.5868</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.6600199999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.57335</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.6855</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.66069</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.65887</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.58108</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.55237</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42667</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75259</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49536</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51312</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5215700000000001</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92857</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48168</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.1878</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90058</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.76188</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45695</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49971</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.49138</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.55028</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75218</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42762</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5175599999999999</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.69835</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49811</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40666</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42824</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42272</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56608</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45499</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66861</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45013</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45165</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.63288</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.59793</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.59301</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.03775</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.58131</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.52118</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.49146</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.45759</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5158700000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5448099999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7601100000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76664</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54453</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50101</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7205199999999999</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76089</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5531699999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01841</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.4831</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44354</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09188</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12742</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08068</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11097</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12759</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.0175</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19325</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14153</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13051</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17544</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84176</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19066</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84812</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34025</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90176</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.71233</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75622</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94728</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.51295</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.65204</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.6917000000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.55413</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7594099999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.40569</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.59529</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.62702</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.81455</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.80562</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.63981</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.62212</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.75291</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.7686799999999999</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.63844</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.78367</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.6430499999999999</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.7615499999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.5917899999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.5323099999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.53765</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.5376000000000001</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.59215</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.54706</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.71427</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5941799999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.54723</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.7996599999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.61051</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.09577</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.79436</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.29628</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.35693</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.73833</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66059</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36508</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00312</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.60754</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49941</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.54703</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.59841</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.74827</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.19679</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.70323</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.93401</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.67789</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9557599999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.90039</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76055</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73017</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18378</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18496</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.44578</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.25902</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.6562</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.24072</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29166</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.10642</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.42936</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04003</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.85264</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.8011200000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.26775</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48823</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.55096</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48688</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.53085</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5342899999999999</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.7993400000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.68136</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.66355</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50462</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08248</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.68717</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66498</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.8012899999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.07587</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.18953</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19752</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5466</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15807</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5572999999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57096</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50118</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23495</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46229</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50584</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51103</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46038</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43295</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.54234</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.52018</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.60519</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.76027</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13718</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.8012699999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.6808</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.49111</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46155</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44966</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44619</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.5888099999999999</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48283</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46355</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5525399999999999</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42499</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46108</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.6163200000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.5872200000000001</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.59192</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.61026</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.57159</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46231</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.38768</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.97658</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.61211</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.46153</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.5531699999999999</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.54683</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.54176</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.54144</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.14687</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.7311799999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.20823</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.13374</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69778</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5665399999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49856</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.6576900000000001</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.43305</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80764</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46773</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48964</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10162</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38253</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.05781</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.97439</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52536</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75975</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.5149</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4268</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5587300000000001</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.6215900000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.07438</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6892</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.8031699999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45489</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40328</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52843</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.40365</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.23961</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.08394</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9814299999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.31166</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.63224</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.55062</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49686</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.58241</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7592000000000001</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5501200000000001</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.54818</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.23282</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.7627200000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.76019</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5833400000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49735</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.00889</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.7703099999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6266900000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75934</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.19948</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6075700000000001</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.74717</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.6369900000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.26292</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.89695</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.88146</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.90211</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.92069</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17282</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.64908</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9551000000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.69211</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9808600000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.65279</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.67149</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.75608</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.65327</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26111</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04319</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02088</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.0306</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.54315</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36105</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.05705</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75926</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34549</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55932</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8066599999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.55235</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75607</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75789</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56188</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.47055</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40567</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.63674</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59505</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5628099999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54212</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48042</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.4993</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5599700000000001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81336</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17367</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.13114</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.04404</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.13387</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.74601</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74076</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.05488</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.07324</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.6814</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55474</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5611799999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.55929</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47958</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48113</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5494</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55069</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54598</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.66134</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55383</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05094</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6616599999999999</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54961</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49958</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49987</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48259</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49974</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48225</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.50001</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5778799999999999</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.56133</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5139</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5004700000000001</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.56131</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66115</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17187</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.07526</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.66188</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58325</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.16311</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.87014</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.66138</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.15981</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83397</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49644</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5117699999999999</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49918</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43981</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5351</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34451</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.9204199999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.6921799999999999</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.69967</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.00739</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.6795399999999999</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.48085</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6294099999999999</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42313</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64046</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.02714</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.20964</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9325399999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.98264</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.0304</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.97324</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.94045</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.97093</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.95397</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.94086</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.4477</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.78737</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.15792</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.72751</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.15405</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.24221</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.22406</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.72348</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.94411</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.86436</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9312999999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54825</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.68703</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.70958</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.75793</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.20874</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.08899</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.02864</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.34042</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.02411</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.12307</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.9279400000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.76225</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.76144</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8215800000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70438</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.56908</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69196</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7385</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6977300000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.75852</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7079099999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46489</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.74713</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5235599999999999</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50993</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.01982</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.9174099999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03045</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.9267300000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.03828</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02111</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02129</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.30168</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09113</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.22768</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.58102</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.6785800000000001</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.61982</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.73402</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7194299999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02348</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.71846</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77148</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14696</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.35714</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.56901</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.79198</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.33639</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.50069</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.10531</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.53794</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.51718</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.79158</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.55907</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.56088</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81209</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7664299999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80738</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.46807</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75928</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49969</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8093400000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31039</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.0018</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.93191</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.95814</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03573</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16369</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06879</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86215</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6924</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.23518</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.2129</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21405</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14844</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86472</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7014199999999999</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09351</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10486</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.1049</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13311</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10255</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.19792</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.6543600000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.58339</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15259</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.74539</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6766</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18216</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8712300000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.08665</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.07312</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.10574</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.0381</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06704</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12546</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04852</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05912</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18289</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16161</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.27639</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20182</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29243</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16774</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.19815</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11792</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09855</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12453</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17417</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19167</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17232</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.10557</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6869400000000001</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.62451</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57359</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.55462</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37557</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.54292</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31071</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.30814</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06558</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51939</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.46893</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.46768</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.48639</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.48766</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.49484</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.48878</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.48724</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.46717</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.45732</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.46346</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8480700000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.57494</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.6974199999999999</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.71302</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.6644099999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.95345</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7650399999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.9588</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17067</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.32324</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.46645</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.45372</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45677</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.56513</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.26451</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8505499999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.78997</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73588</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70005</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50169</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84377</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.87952</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.23926</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77497</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57938</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58425</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.64063</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.7229500000000001</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.6009500000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.74852</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.62327</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.21258</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.18741</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41668</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.18926</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.18638</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.19313</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.12233</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.09668</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20687</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.12379</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.20993</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.07036</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.10023</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20588</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.10446</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.55057</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80971</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80376</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56389</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.22799</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84876</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8492499999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5589500000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55443</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56288</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51537</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55379</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52107</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50113</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45965</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45989</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49497</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49903</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54745</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52018</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55714</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17486</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88246</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49287</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.19574</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50838</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56984</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84446</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7954600000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59712</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85202</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50387</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5215700000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54522</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17623</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70052</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55468</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.18027</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54862</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.54938</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58035</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79908</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55426</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79745</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.84853</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17337</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7981</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6831499999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.07874</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17471</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17883</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.18221</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.18004</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8224400000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7347100000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.65246</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.68338</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.69178</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7330599999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8334</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81676</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.62051</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.81387</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.76302</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.14237</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.7633799999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60903</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.64778</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64466</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.61975</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61586</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.71661</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67701</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8252</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70387</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6080099999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53091</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
